--- a/artfynd/A 25040-2025 artfynd.xlsx
+++ b/artfynd/A 25040-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126410909</v>
       </c>
       <c r="B2" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126410548</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126409398</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126410421</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126410461</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>126410710</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126409620</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>126410604</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>126410474</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,27 +1648,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126410933</v>
+        <v>126410757</v>
       </c>
       <c r="B11" t="n">
-        <v>58025</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1677,16 +1677,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Märramyran, Märramyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583295</v>
+        <v>583319</v>
       </c>
       <c r="R11" t="n">
-        <v>7179114</v>
+        <v>7179154</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,27 +1760,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126410757</v>
+        <v>126410933</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>58027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1784,21 +1789,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Märramyran, Märramyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583319</v>
+        <v>583295</v>
       </c>
       <c r="R12" t="n">
-        <v>7179154</v>
+        <v>7179114</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 25040-2025 artfynd.xlsx
+++ b/artfynd/A 25040-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126410909</v>
+        <v>126409322</v>
       </c>
       <c r="B2" t="n">
-        <v>82792</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Märramyran, Märramyran, Ås lm</t>
+          <t>Stormyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583295</v>
+        <v>583528</v>
       </c>
       <c r="R2" t="n">
-        <v>7179114</v>
+        <v>7179036</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126410548</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126409398</v>
+        <v>126410909</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyran, Ås lm</t>
+          <t>Märramyran, Märramyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583505</v>
+        <v>583295</v>
       </c>
       <c r="R4" t="n">
-        <v>7179051</v>
+        <v>7179114</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,11 +999,11 @@
         <v>126410421</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126410461</v>
+        <v>126410474</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
         <v>7179065</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126410710</v>
+        <v>126409620</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583338</v>
+        <v>583467</v>
       </c>
       <c r="R7" t="n">
-        <v>7179130</v>
+        <v>7179042</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126409620</v>
+        <v>126410710</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583467</v>
+        <v>583338</v>
       </c>
       <c r="R8" t="n">
-        <v>7179042</v>
+        <v>7179130</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,45 +1434,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126410604</v>
+        <v>126410757</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ås lm</t>
+          <t>Märramyran, Märramyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583489</v>
+        <v>583319</v>
       </c>
       <c r="R9" t="n">
-        <v>7179069</v>
+        <v>7179154</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,48 +1546,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126410474</v>
+        <v>126410933</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ås lm</t>
+          <t>Märramyran, Märramyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583466</v>
+        <v>583295</v>
       </c>
       <c r="R10" t="n">
-        <v>7179065</v>
+        <v>7179114</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,50 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126410757</v>
+        <v>126410604</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Märramyran, Märramyran, Ås lm</t>
+          <t>Stormyran, Stormyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583319</v>
+        <v>583489</v>
       </c>
       <c r="R11" t="n">
-        <v>7179154</v>
+        <v>7179069</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1757,113 +1757,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>126410933</v>
-      </c>
-      <c r="B12" t="n">
-        <v>58027</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Märramyran, Märramyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>583295</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7179114</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Tove Lundmark</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Tove Lundmark</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
